--- a/C++kadai/kadai04.xlsx
+++ b/C++kadai/kadai04.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\OracleLinux_8_5\home\integral\c++\repo\C++kadai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C5E2CD-F59C-4BE5-8598-FFAFCEFA1CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145E4922-0E11-435C-B723-5CD3622E8CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{6403A9A6-ECE0-481A-9546-5B7FA10BFF51}"/>
   </bookViews>
@@ -2059,15 +2059,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>685799</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>235323</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1120</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>137</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2085,8 +2085,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7543799" y="1683123"/>
-          <a:ext cx="1" cy="24529677"/>
+          <a:off x="7520267" y="1669676"/>
+          <a:ext cx="10086" cy="30592059"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2121,15 +2121,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>617054</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>231086</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>55079</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>97735</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2144,7 +2144,136 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7486650" y="15268575"/>
+          <a:off x="7475054" y="19538261"/>
+          <a:ext cx="123825" cy="2724149"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="28" name="直線コネクタ 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40A231B6-8184-B31C-C872-55E1845F4AEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="21" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10253383" y="1669676"/>
+          <a:ext cx="11205" cy="30603265"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>607529</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>21535</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>45554</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>126310</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="251" name="正方形/長方形 250">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9E1A9E4-2E0A-1131-3702-B3CA028836DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10208729" y="26710585"/>
           <a:ext cx="123825" cy="2724150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2188,145 +2317,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>235323</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="28" name="直線コネクタ 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40A231B6-8184-B31C-C872-55E1845F4AEF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="21" idx="2"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10287000" y="1683123"/>
-          <a:ext cx="0" cy="24539202"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="dk1"/>
-          </a:solidFill>
-          <a:prstDash val="dash"/>
-          <a:round/>
-          <a:headEnd type="none" w="med" len="med"/>
-          <a:tailEnd type="none" w="med" len="med"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="251" name="正方形/長方形 250">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9E1A9E4-2E0A-1131-3702-B3CA028836DE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10229850" y="20993100"/>
-          <a:ext cx="123825" cy="2724150"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:sysClr val="window" lastClr="FFFFFF"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:sysClr val="windowText" lastClr="000000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>684679</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>235323</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2343,8 +2343,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4799479" y="1683123"/>
-          <a:ext cx="1121" cy="24539202"/>
+          <a:off x="4784912" y="1669676"/>
+          <a:ext cx="11206" cy="30614471"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2379,15 +2379,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:colOff>636933</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>16565</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>74958</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>35616</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2402,8 +2402,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4743450" y="6438900"/>
-          <a:ext cx="123825" cy="3352800"/>
+          <a:off x="4761672" y="7959587"/>
+          <a:ext cx="125482" cy="3381790"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2957,15 +2957,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
+      <xdr:colOff>313765</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>115</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>145677</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2980,8 +2980,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="3076575" y="1562100"/>
-          <a:ext cx="9525" cy="25974675"/>
+          <a:off x="3048000" y="1548653"/>
+          <a:ext cx="29135" cy="31329406"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3016,15 +3016,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:colOff>17808</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>16565</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>662828</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:colOff>671111</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>16565</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3039,8 +3039,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="695325" y="10010775"/>
-          <a:ext cx="10940303" cy="0"/>
+          <a:off x="705265" y="11562522"/>
+          <a:ext cx="10965150" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3075,15 +3075,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:colOff>341658</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>4970</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>4763</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:colOff>13046</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>4970</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -3098,8 +3098,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3076575" y="6200775"/>
-          <a:ext cx="1728788" cy="238125"/>
+          <a:off x="3063087" y="7842684"/>
+          <a:ext cx="1712459" cy="244929"/>
           <a:chOff x="3086100" y="5257800"/>
           <a:chExt cx="1728788" cy="238125"/>
         </a:xfrm>
@@ -3211,13 +3211,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>235323</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>137</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3233,8 +3233,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1924050"/>
-          <a:ext cx="10972800" cy="24288750"/>
+          <a:off x="683559" y="1904999"/>
+          <a:ext cx="10936941" cy="30356736"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3278,13 +3278,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>171449</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>114</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>347383</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>134470</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3299,8 +3299,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3028950" y="1857375"/>
-          <a:ext cx="95250" cy="25422225"/>
+          <a:off x="3019985" y="1841125"/>
+          <a:ext cx="61633" cy="30790404"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3367,8 +3367,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="685800" y="1924050"/>
-          <a:ext cx="2057400" cy="714376"/>
+          <a:off x="680357" y="1959429"/>
+          <a:ext cx="2041072" cy="734786"/>
           <a:chOff x="685800" y="1924049"/>
           <a:chExt cx="2057400" cy="714376"/>
         </a:xfrm>
@@ -3494,15 +3494,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>89808</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>217714</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>13608</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>227238</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3517,8 +3517,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1447800" y="4543425"/>
-          <a:ext cx="1295400" cy="247650"/>
+          <a:off x="1450522" y="4626428"/>
+          <a:ext cx="1284515" cy="254453"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3567,16 +3567,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>676276</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>58629</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>234282</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>676276</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>58628</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>234281</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3591,8 +3591,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1362076" y="10248900"/>
-          <a:ext cx="1371600" cy="238125"/>
+          <a:off x="1419343" y="11990853"/>
+          <a:ext cx="1360714" cy="244928"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3642,15 +3642,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>397565</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>3314</xdr:rowOff>
+      <xdr:colOff>385969</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>226945</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>4763</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>680624</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>231086</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3667,8 +3667,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3140765" y="15262364"/>
-          <a:ext cx="4407798" cy="6211"/>
+          <a:off x="3129169" y="19534120"/>
+          <a:ext cx="4409455" cy="4141"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3697,15 +3697,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>1361</xdr:rowOff>
+      <xdr:colOff>102704</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>224992</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:colOff>426554</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>202510</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3720,8 +3720,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4914900" y="15022286"/>
-          <a:ext cx="2381250" cy="217714"/>
+          <a:off x="4903304" y="19294042"/>
+          <a:ext cx="2381250" cy="215643"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3782,15 +3782,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>202510</xdr:colOff>
-      <xdr:row>114</xdr:row>
-      <xdr:rowOff>229429</xdr:rowOff>
+      <xdr:colOff>181389</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>233985</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>469210</xdr:colOff>
-      <xdr:row>116</xdr:row>
-      <xdr:rowOff>31474</xdr:rowOff>
+      <xdr:colOff>448089</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>33959</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -3805,8 +3805,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2945710" y="27394729"/>
-          <a:ext cx="266700" cy="278295"/>
+          <a:off x="2902818" y="34034128"/>
+          <a:ext cx="266700" cy="289831"/>
           <a:chOff x="2955235" y="15336079"/>
           <a:chExt cx="266700" cy="278295"/>
         </a:xfrm>
@@ -3887,15 +3887,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>680416</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>668820</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>2485</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>20292</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>675861</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>3727</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3910,8 +3910,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="1366216" y="18373725"/>
-          <a:ext cx="10292384" cy="1242"/>
+          <a:off x="1354620" y="22643410"/>
+          <a:ext cx="10294041" cy="1242"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -3969,8 +3969,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3129424" y="2155965"/>
-          <a:ext cx="1212320" cy="487917"/>
+          <a:off x="3107653" y="2191344"/>
+          <a:ext cx="1201434" cy="508327"/>
           <a:chOff x="3078071" y="2170044"/>
           <a:chExt cx="1215633" cy="494129"/>
         </a:xfrm>
@@ -4196,8 +4196,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3121142" y="2876551"/>
-          <a:ext cx="1212320" cy="489988"/>
+          <a:off x="3099371" y="2939144"/>
+          <a:ext cx="1201434" cy="503595"/>
           <a:chOff x="3078071" y="2170044"/>
           <a:chExt cx="1215633" cy="494129"/>
         </a:xfrm>
@@ -4401,13 +4401,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>235323</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>137</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -4423,10 +4423,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1371600" y="3590925"/>
-          <a:ext cx="10287000" cy="22621875"/>
-          <a:chOff x="1371600" y="4060435"/>
-          <a:chExt cx="10972800" cy="13817990"/>
+          <a:off x="1360714" y="3664323"/>
+          <a:ext cx="10205357" cy="29890891"/>
+          <a:chOff x="1371600" y="4060434"/>
+          <a:chExt cx="10972800" cy="13817991"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
@@ -4493,10 +4493,10 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="1371600" y="4060435"/>
-            <a:ext cx="1463040" cy="505535"/>
+            <a:off x="1371600" y="4060434"/>
+            <a:ext cx="1463040" cy="363630"/>
             <a:chOff x="685800" y="1917310"/>
-            <a:chExt cx="2194560" cy="505536"/>
+            <a:chExt cx="2194560" cy="363631"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
@@ -4513,7 +4513,7 @@
           <xdr:spPr>
             <a:xfrm rot="10800000" flipH="1">
               <a:off x="685800" y="1924050"/>
-              <a:ext cx="2194560" cy="498796"/>
+              <a:ext cx="2194560" cy="356891"/>
             </a:xfrm>
             <a:prstGeom prst="snip1Rect">
               <a:avLst>
@@ -4572,7 +4572,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="685800" y="1917310"/>
-              <a:ext cx="2194560" cy="498797"/>
+              <a:ext cx="2194560" cy="363631"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -4635,7 +4635,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>346213</xdr:colOff>
+      <xdr:colOff>489856</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>20779</xdr:rowOff>
     </xdr:to>
@@ -4652,10 +4652,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3129424" y="3834020"/>
-          <a:ext cx="1331589" cy="492059"/>
+          <a:off x="3107653" y="3923827"/>
+          <a:ext cx="1464346" cy="505666"/>
           <a:chOff x="3078071" y="2170044"/>
-          <a:chExt cx="1335228" cy="494129"/>
+          <a:chExt cx="1480451" cy="494129"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
@@ -4814,7 +4814,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="3152563" y="2170044"/>
-            <a:ext cx="1260736" cy="249721"/>
+            <a:ext cx="1405959" cy="234484"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -4879,8 +4879,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3121142" y="4533901"/>
-          <a:ext cx="1212320" cy="489988"/>
+          <a:off x="3099371" y="4637315"/>
+          <a:ext cx="1201434" cy="510399"/>
           <a:chOff x="3078071" y="2170044"/>
           <a:chExt cx="1215633" cy="494129"/>
         </a:xfrm>
@@ -5083,15 +5083,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>404606</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>180976</xdr:rowOff>
+      <xdr:colOff>381001</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>207066</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>636934</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>54665</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -5106,10 +5106,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3147806" y="6629401"/>
-          <a:ext cx="1595644" cy="561974"/>
-          <a:chOff x="3147683" y="4972051"/>
-          <a:chExt cx="1595767" cy="561974"/>
+          <a:off x="3102430" y="8289709"/>
+          <a:ext cx="1616647" cy="582385"/>
+          <a:chOff x="3115858" y="4972051"/>
+          <a:chExt cx="1627592" cy="561974"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp macro="">
@@ -5125,8 +5125,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3147683" y="5496342"/>
-            <a:ext cx="1595767" cy="9109"/>
+            <a:off x="3115858" y="5504534"/>
+            <a:ext cx="1627592" cy="917"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -5227,15 +5227,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>396322</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>228610</xdr:rowOff>
+      <xdr:colOff>404605</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>16576</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>628649</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>236894</xdr:rowOff>
+      <xdr:colOff>636932</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>24860</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -5250,8 +5250,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3139522" y="7391410"/>
-          <a:ext cx="1603927" cy="246409"/>
+          <a:off x="3126034" y="9078933"/>
+          <a:ext cx="1593041" cy="253213"/>
           <a:chOff x="3148941" y="6448424"/>
           <a:chExt cx="1604034" cy="246267"/>
         </a:xfrm>
@@ -5356,15 +5356,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>381076</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>171451</xdr:rowOff>
+      <xdr:colOff>386952</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>197542</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>636932</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -5379,10 +5379,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3124276" y="7810501"/>
-          <a:ext cx="1619174" cy="561974"/>
-          <a:chOff x="3124200" y="4972051"/>
-          <a:chExt cx="1619250" cy="561974"/>
+          <a:off x="3108381" y="9504828"/>
+          <a:ext cx="1610694" cy="608680"/>
+          <a:chOff x="3121790" y="4972051"/>
+          <a:chExt cx="1621660" cy="588270"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:cxnSp macro="">
@@ -5398,8 +5398,8 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm flipV="1">
-            <a:off x="3147683" y="5505450"/>
-            <a:ext cx="1595767" cy="8505"/>
+            <a:off x="3121790" y="5505450"/>
+            <a:ext cx="1621660" cy="1293"/>
           </a:xfrm>
           <a:prstGeom prst="straightConnector1">
             <a:avLst/>
@@ -5437,7 +5437,7 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="3124200" y="4972051"/>
-            <a:ext cx="1562100" cy="561974"/>
+            <a:ext cx="1562100" cy="588270"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -5500,15 +5500,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>396322</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>228599</xdr:rowOff>
+      <xdr:colOff>404605</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>14494</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>628649</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>228600</xdr:rowOff>
+      <xdr:colOff>636932</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>16566</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -5523,8 +5523,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3139522" y="8582024"/>
-          <a:ext cx="1603927" cy="238126"/>
+          <a:off x="3126034" y="10301494"/>
+          <a:ext cx="1593041" cy="247001"/>
           <a:chOff x="3148941" y="6448424"/>
           <a:chExt cx="1604034" cy="238126"/>
         </a:xfrm>
@@ -5629,15 +5629,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>376698</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>228601</xdr:rowOff>
+      <xdr:colOff>375456</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>7042</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>279537</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>4214</xdr:rowOff>
+      <xdr:colOff>278295</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>20780</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -5652,8 +5652,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3119898" y="9058276"/>
-          <a:ext cx="1274439" cy="489988"/>
+          <a:off x="3096885" y="10783899"/>
+          <a:ext cx="1263553" cy="503595"/>
           <a:chOff x="3078071" y="2170044"/>
           <a:chExt cx="1277922" cy="494129"/>
         </a:xfrm>
@@ -5856,15 +5856,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>369659</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>228601</xdr:rowOff>
+      <xdr:colOff>377942</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>7042</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>329648</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>4214</xdr:rowOff>
+      <xdr:colOff>549889</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>11738</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -5879,10 +5879,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3112859" y="10248901"/>
-          <a:ext cx="1331589" cy="489988"/>
+          <a:off x="3099371" y="12008542"/>
+          <a:ext cx="1532661" cy="2453982"/>
           <a:chOff x="3078071" y="2170044"/>
-          <a:chExt cx="1335228" cy="494129"/>
+          <a:chExt cx="1549063" cy="2405363"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
@@ -6041,7 +6041,57 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="3152563" y="2170044"/>
-            <a:ext cx="1260736" cy="249721"/>
+            <a:ext cx="1373063" cy="233415"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+              <a:t>縦長入力を要求</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="369" name="テキスト ボックス 368">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4B51C6D-2851-CE9F-A1CF-CA13251BDE4D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3254071" y="4341992"/>
+            <a:ext cx="1373063" cy="233415"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6083,15 +6133,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>413556</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>370902</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>234398</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>373545</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>13739</xdr:rowOff>
+      <xdr:colOff>645138</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>190389</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6106,10 +6156,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3156756" y="12639676"/>
-          <a:ext cx="1331589" cy="489988"/>
+          <a:off x="3092331" y="15909827"/>
+          <a:ext cx="1634950" cy="2405276"/>
           <a:chOff x="3078071" y="2170044"/>
-          <a:chExt cx="1335228" cy="494129"/>
+          <a:chExt cx="1652507" cy="2369380"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
@@ -6268,7 +6318,57 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="3152563" y="2170044"/>
-            <a:ext cx="1260736" cy="249721"/>
+            <a:ext cx="1476477" cy="207795"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+              <a:t>横長入力を要求</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="370" name="テキスト ボックス 369">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39A6D11C-B0BA-C587-8F35-0FE86B295E63}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3254101" y="4331629"/>
+            <a:ext cx="1476477" cy="207795"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -6310,15 +6410,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>383739</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>222389</xdr:rowOff>
+      <xdr:colOff>382497</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>217834</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>224459</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>234056</xdr:rowOff>
+      <xdr:colOff>223217</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>231572</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6333,8 +6433,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3126939" y="10957064"/>
-          <a:ext cx="1212320" cy="487917"/>
+          <a:off x="3103926" y="12709191"/>
+          <a:ext cx="1201434" cy="503595"/>
           <a:chOff x="3078071" y="2170044"/>
           <a:chExt cx="1215633" cy="494129"/>
         </a:xfrm>
@@ -6537,15 +6637,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>421839</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>4970</xdr:rowOff>
+      <xdr:colOff>370901</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>1243</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>262559</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>20779</xdr:rowOff>
+      <xdr:colOff>211621</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>14982</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6560,8 +6660,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3165039" y="13359020"/>
-          <a:ext cx="1212320" cy="492059"/>
+          <a:off x="3092330" y="16656386"/>
+          <a:ext cx="1201434" cy="503596"/>
           <a:chOff x="3078071" y="2170044"/>
           <a:chExt cx="1215633" cy="494129"/>
         </a:xfrm>
@@ -6764,15 +6864,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>400303</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>3315</xdr:rowOff>
+      <xdr:colOff>388707</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>226945</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>303142</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>14982</xdr:rowOff>
+      <xdr:colOff>291546</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>236542</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -6787,8 +6887,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3143503" y="17405490"/>
-          <a:ext cx="1274439" cy="487917"/>
+          <a:off x="3110136" y="22270516"/>
+          <a:ext cx="1263553" cy="499455"/>
           <a:chOff x="3078071" y="2170044"/>
           <a:chExt cx="1277922" cy="494129"/>
         </a:xfrm>
@@ -6991,15 +7091,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>414131</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>28560</xdr:rowOff>
+      <xdr:colOff>402535</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>11995</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>11581</xdr:rowOff>
+      <xdr:colOff>617054</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>233141</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7014,8 +7114,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3157331" y="16001985"/>
-          <a:ext cx="4329319" cy="221146"/>
+          <a:off x="3123964" y="20830924"/>
+          <a:ext cx="4296661" cy="221146"/>
           <a:chOff x="423538" y="6467474"/>
           <a:chExt cx="4329437" cy="219161"/>
         </a:xfrm>
@@ -7120,15 +7220,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>414131</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>238116</xdr:rowOff>
+      <xdr:colOff>402535</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>223622</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>17799</xdr:rowOff>
+      <xdr:colOff>626579</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>1234</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7143,8 +7243,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3157331" y="16925916"/>
-          <a:ext cx="4338844" cy="255933"/>
+          <a:off x="3123964" y="21777336"/>
+          <a:ext cx="4306186" cy="267469"/>
           <a:chOff x="413950" y="6438899"/>
           <a:chExt cx="4339025" cy="255953"/>
         </a:xfrm>
@@ -7249,15 +7349,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>397565</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>76201</xdr:rowOff>
+      <xdr:colOff>385969</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>59637</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>637761</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>626165</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>145360</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7272,8 +7372,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3140765" y="15335251"/>
-          <a:ext cx="4354996" cy="561974"/>
+          <a:off x="3107398" y="20143780"/>
+          <a:ext cx="4322338" cy="575580"/>
           <a:chOff x="397463" y="4857751"/>
           <a:chExt cx="4355099" cy="561974"/>
         </a:xfrm>
@@ -7393,15 +7493,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>414131</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:colOff>402535</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>107260</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>636104</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>59635</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7416,8 +7516,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3157331" y="16335375"/>
-          <a:ext cx="4348369" cy="428625"/>
+          <a:off x="3123964" y="21171117"/>
+          <a:ext cx="4315711" cy="442232"/>
           <a:chOff x="404531" y="5416551"/>
           <a:chExt cx="4348444" cy="380999"/>
         </a:xfrm>
@@ -7537,15 +7637,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>395081</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>373960</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>4556</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>655154</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>12010</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7560,8 +7660,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3138281" y="20735925"/>
-          <a:ext cx="7139194" cy="247650"/>
+          <a:off x="3095389" y="27191627"/>
+          <a:ext cx="7084765" cy="252383"/>
           <a:chOff x="3176154" y="5248275"/>
           <a:chExt cx="7139421" cy="247650"/>
         </a:xfrm>
@@ -7672,15 +7772,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>383739</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>8283</xdr:rowOff>
+      <xdr:colOff>372142</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>229843</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>343728</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>22021</xdr:rowOff>
+      <xdr:colOff>598712</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>7798</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7695,10 +7795,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3126939" y="18601083"/>
-          <a:ext cx="1331589" cy="489988"/>
+          <a:off x="3093571" y="23498057"/>
+          <a:ext cx="1587284" cy="2472170"/>
           <a:chOff x="3078071" y="2170044"/>
-          <a:chExt cx="1335228" cy="494129"/>
+          <a:chExt cx="1603862" cy="2428160"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
@@ -7857,7 +7957,57 @@
         <xdr:spPr>
           <a:xfrm>
             <a:off x="3152563" y="2170044"/>
-            <a:ext cx="1260736" cy="249721"/>
+            <a:ext cx="1337654" cy="278073"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="9525" cmpd="sng">
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+              <a:t>長さ入力を要求</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="371" name="テキスト ボックス 370">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51380D70-E413-F7D6-4678-0D15CD4DD30A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3344279" y="4320131"/>
+            <a:ext cx="1337654" cy="278073"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7899,15 +8049,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>400304</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>8284</xdr:rowOff>
+      <xdr:colOff>388708</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>229844</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>241024</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>22022</xdr:rowOff>
+      <xdr:colOff>229428</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>5457</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -7922,8 +8072,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3143504" y="19315459"/>
-          <a:ext cx="1212320" cy="489988"/>
+          <a:off x="3110137" y="24232844"/>
+          <a:ext cx="1201434" cy="510399"/>
           <a:chOff x="3078071" y="2170044"/>
           <a:chExt cx="1215633" cy="494129"/>
         </a:xfrm>
@@ -8126,15 +8276,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>386799</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>76201</xdr:rowOff>
+      <xdr:colOff>365678</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>78686</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>609601</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>588480</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>164410</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -8149,8 +8299,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3129999" y="21050251"/>
-          <a:ext cx="7080802" cy="561974"/>
+          <a:off x="3087107" y="27510686"/>
+          <a:ext cx="7026373" cy="575581"/>
           <a:chOff x="3158406" y="5086351"/>
           <a:chExt cx="7080969" cy="561974"/>
         </a:xfrm>
@@ -8270,15 +8420,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>395081</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>228599</xdr:rowOff>
+      <xdr:colOff>373960</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>231084</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>617054</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>21535</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -8293,8 +8443,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3138281" y="21678899"/>
-          <a:ext cx="7101094" cy="266701"/>
+          <a:off x="3095389" y="28152941"/>
+          <a:ext cx="7046665" cy="280308"/>
           <a:chOff x="3176195" y="6438899"/>
           <a:chExt cx="7101280" cy="266701"/>
         </a:xfrm>
@@ -8399,15 +8549,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>395081</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>114301</xdr:rowOff>
+      <xdr:colOff>373960</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>116786</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>588479</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>116785</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -8422,8 +8572,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3138281" y="22040851"/>
-          <a:ext cx="7072519" cy="476249"/>
+          <a:off x="3095389" y="28528500"/>
+          <a:ext cx="7018090" cy="489856"/>
           <a:chOff x="3128657" y="5143501"/>
           <a:chExt cx="7072618" cy="476249"/>
         </a:xfrm>
@@ -8543,15 +8693,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>395080</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>228599</xdr:rowOff>
+      <xdr:colOff>373959</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>231084</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>619124</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>598003</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>12010</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -8566,8 +8716,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3138280" y="22631399"/>
-          <a:ext cx="7082044" cy="257176"/>
+          <a:off x="3095388" y="29132655"/>
+          <a:ext cx="7027615" cy="270784"/>
           <a:chOff x="3166691" y="6438899"/>
           <a:chExt cx="7082209" cy="257176"/>
         </a:xfrm>
@@ -8672,15 +8822,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>365931</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>14495</xdr:rowOff>
+      <xdr:colOff>344810</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>16980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>268770</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>30304</xdr:rowOff>
+      <xdr:colOff>247649</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>32789</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -8695,8 +8845,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3109131" y="23131670"/>
-          <a:ext cx="1274439" cy="492059"/>
+          <a:off x="3066239" y="29653337"/>
+          <a:ext cx="1263553" cy="505666"/>
           <a:chOff x="3078071" y="2170044"/>
           <a:chExt cx="1277922" cy="494129"/>
         </a:xfrm>
@@ -8899,15 +9049,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>47626</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:colOff>37686</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>202510</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>47626</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:colOff>37686</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>202510</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8922,7 +9072,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1419226" y="18573750"/>
+          <a:off x="1409286" y="22843435"/>
           <a:ext cx="1371600" cy="238125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8973,15 +9123,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>670891</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>649770</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>4556</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>1242</xdr:rowOff>
+      <xdr:colOff>655154</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>5798</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -8996,7 +9146,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="1356691" y="24069675"/>
+          <a:off x="1335570" y="29789231"/>
           <a:ext cx="10292384" cy="1242"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -9031,16 +9181,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>19051</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>685386</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>12010</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>19051</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>685386</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>12010</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9055,7 +9205,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1390651" y="24317325"/>
+          <a:off x="1371186" y="30034810"/>
           <a:ext cx="1371600" cy="238125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -9106,15 +9256,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>374214</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>353093</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>4556</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>334203</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>13739</xdr:rowOff>
+      <xdr:colOff>313082</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>16224</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -9129,8 +9279,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3117414" y="24307801"/>
-          <a:ext cx="1331589" cy="489988"/>
+          <a:off x="3074522" y="30865556"/>
+          <a:ext cx="1320703" cy="501525"/>
           <a:chOff x="3078071" y="2170044"/>
           <a:chExt cx="1335228" cy="494129"/>
         </a:xfrm>
@@ -9336,16 +9486,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>4141</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>670476</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>4556</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>1242</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>675861</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>5798</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -9360,8 +9510,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="1375741" y="25260300"/>
-          <a:ext cx="10292384" cy="1242"/>
+          <a:off x="1356276" y="30979856"/>
+          <a:ext cx="10292385" cy="1242"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -9396,15 +9546,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>645629</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>12011</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>342899</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:colOff>321778</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>12010</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9419,8 +9569,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1352550" y="25507950"/>
-          <a:ext cx="1733549" cy="238125"/>
+          <a:off x="1331429" y="31225436"/>
+          <a:ext cx="1733549" cy="238124"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9486,15 +9636,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>375457</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>8283</xdr:rowOff>
+      <xdr:colOff>354336</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>10769</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>335446</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>22021</xdr:rowOff>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>24506</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -9509,8 +9659,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3118657" y="25506708"/>
-          <a:ext cx="1331589" cy="489988"/>
+          <a:off x="3075765" y="32096412"/>
+          <a:ext cx="1320703" cy="503594"/>
           <a:chOff x="3078071" y="2170044"/>
           <a:chExt cx="1335228" cy="494129"/>
         </a:xfrm>
@@ -9713,22 +9863,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
+      <xdr:colOff>6147</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>167265</xdr:rowOff>
+      <xdr:rowOff>39294</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>676272</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>228599</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="261" name="グループ化 260">
+        <xdr:cNvPr id="250" name="グループ化 249">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EC552D9-8608-C0B6-2E62-FB4C03A5F4B8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C540F259-CCBA-23E5-C12E-D9E30E1C7D8B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9736,18 +9886,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1447800" y="5186940"/>
-          <a:ext cx="4029075" cy="956685"/>
-          <a:chOff x="1447800" y="5186940"/>
-          <a:chExt cx="4029075" cy="956685"/>
+          <a:off x="1366861" y="5182794"/>
+          <a:ext cx="4071911" cy="2393662"/>
+          <a:chOff x="1377553" y="5057489"/>
+          <a:chExt cx="4099321" cy="2333911"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="260" name="グループ化 259">
+          <xdr:cNvPr id="261" name="グループ化 260">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45B36529-285D-9172-2B65-BE15FADE32F8}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EC552D9-8608-C0B6-2E62-FB4C03A5F4B8}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -9755,10 +9905,10 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="1447800" y="5186940"/>
-            <a:ext cx="4029075" cy="956685"/>
-            <a:chOff x="1581150" y="5148840"/>
-            <a:chExt cx="3905251" cy="956685"/>
+            <a:off x="1377553" y="5057489"/>
+            <a:ext cx="4099321" cy="2333911"/>
+            <a:chOff x="1377553" y="5057489"/>
+            <a:chExt cx="4099321" cy="2333911"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:grpSp>
@@ -9774,10 +9924,10 @@
           </xdr:nvGrpSpPr>
           <xdr:grpSpPr>
             <a:xfrm>
-              <a:off x="1600201" y="5148840"/>
-              <a:ext cx="3886200" cy="956685"/>
-              <a:chOff x="559971" y="-278814"/>
-              <a:chExt cx="10999316" cy="13811251"/>
+              <a:off x="1377553" y="5057489"/>
+              <a:ext cx="4099321" cy="2333911"/>
+              <a:chOff x="313335" y="-2147646"/>
+              <a:chExt cx="11245952" cy="33693676"/>
             </a:xfrm>
           </xdr:grpSpPr>
           <xdr:sp macro="" textlink="">
@@ -9793,8 +9943,8 @@
             </xdr:nvSpPr>
             <xdr:spPr>
               <a:xfrm>
-                <a:off x="702080" y="-278814"/>
-                <a:ext cx="10857207" cy="13811251"/>
+                <a:off x="543046" y="-278814"/>
+                <a:ext cx="11016241" cy="31824844"/>
               </a:xfrm>
               <a:prstGeom prst="rect">
                 <a:avLst/>
@@ -9844,10 +9994,10 @@
             </xdr:nvGrpSpPr>
             <xdr:grpSpPr>
               <a:xfrm>
-                <a:off x="559971" y="-218394"/>
-                <a:ext cx="2952991" cy="6875416"/>
-                <a:chOff x="-531643" y="-2361527"/>
-                <a:chExt cx="4429486" cy="6875430"/>
+                <a:off x="313335" y="-2147646"/>
+                <a:ext cx="4545567" cy="10881430"/>
+                <a:chOff x="-901595" y="-4290783"/>
+                <a:chExt cx="6818350" cy="10881452"/>
               </a:xfrm>
             </xdr:grpSpPr>
             <xdr:sp macro="" textlink="">
@@ -9863,12 +10013,12 @@
               </xdr:nvSpPr>
               <xdr:spPr>
                 <a:xfrm rot="10800000" flipH="1">
-                  <a:off x="-298957" y="-2361527"/>
-                  <a:ext cx="3983567" cy="6875430"/>
+                  <a:off x="-557030" y="-2361557"/>
+                  <a:ext cx="6196350" cy="7806644"/>
                 </a:xfrm>
                 <a:prstGeom prst="snip1Rect">
                   <a:avLst>
-                    <a:gd name="adj" fmla="val 27778"/>
+                    <a:gd name="adj" fmla="val 21489"/>
                   </a:avLst>
                 </a:prstGeom>
                 <a:solidFill>
@@ -9922,8 +10072,8 @@
               </xdr:nvSpPr>
               <xdr:spPr>
                 <a:xfrm rot="10800000" flipV="1">
-                  <a:off x="-531643" y="-1017884"/>
-                  <a:ext cx="4429486" cy="3677391"/>
+                  <a:off x="-901595" y="-4290783"/>
+                  <a:ext cx="6818350" cy="10881452"/>
                 </a:xfrm>
                 <a:prstGeom prst="rect">
                   <a:avLst/>
@@ -9960,7 +10110,18 @@
                         <a:sysClr val="windowText" lastClr="000000"/>
                       </a:solidFill>
                     </a:rPr>
-                    <a:t>alt </a:t>
+                    <a:t>loop</a:t>
+                  </a:r>
+                </a:p>
+                <a:p>
+                  <a:pPr algn="ctr"/>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>[</a:t>
                   </a:r>
                   <a:r>
                     <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
@@ -9968,87 +10129,262 @@
                         <a:sysClr val="windowText" lastClr="000000"/>
                       </a:solidFill>
                     </a:rPr>
-                    <a:t>入力値</a:t>
+                    <a:t>入力値 </a:t>
                   </a:r>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>= - or </a:t>
+                  </a:r>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>文字</a:t>
+                  </a:r>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>]</a:t>
+                  </a:r>
+                  <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:endParaRPr>
                 </a:p>
               </xdr:txBody>
             </xdr:sp>
           </xdr:grpSp>
         </xdr:grpSp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="59" name="テキスト ボックス 58">
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="61" name="グループ化 60">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E49B88B-CEBC-9E17-538D-DB2B4910A07E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{625A996C-05FD-6A3E-F8A7-D541EA264A60}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
             <a:xfrm>
-              <a:off x="1581150" y="5734050"/>
-              <a:ext cx="1476375" cy="247650"/>
+              <a:off x="3137709" y="5237503"/>
+              <a:ext cx="1119967" cy="509039"/>
+              <a:chOff x="3078071" y="2150831"/>
+              <a:chExt cx="1123027" cy="513342"/>
             </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="9525" cmpd="sng">
+          </xdr:grpSpPr>
+          <xdr:grpSp>
+            <xdr:nvGrpSpPr>
+              <xdr:cNvPr id="62" name="グループ化 61">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D91CE40-2F1C-EE9A-EA78-E49A49794E8E}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvGrpSpPr/>
+            </xdr:nvGrpSpPr>
+            <xdr:grpSpPr>
+              <a:xfrm>
+                <a:off x="3078071" y="2407127"/>
+                <a:ext cx="519226" cy="257046"/>
+                <a:chOff x="3111201" y="2183497"/>
+                <a:chExt cx="519226" cy="257046"/>
+              </a:xfrm>
+            </xdr:grpSpPr>
+            <xdr:cxnSp macro="">
+              <xdr:nvCxnSpPr>
+                <xdr:cNvPr id="256" name="直線矢印コネクタ 255">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4DC51FF-D4F2-3F45-5549-824C93C948F6}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvCxnSpPr/>
+              </xdr:nvCxnSpPr>
+              <xdr:spPr>
+                <a:xfrm flipH="1">
+                  <a:off x="3111201" y="2440543"/>
+                  <a:ext cx="518937" cy="0"/>
+                </a:xfrm>
+                <a:prstGeom prst="straightConnector1">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                  <a:round/>
+                  <a:headEnd type="none" w="med" len="med"/>
+                  <a:tailEnd type="triangle" w="med" len="med"/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="tx1"/>
+                </a:fontRef>
+              </xdr:style>
+            </xdr:cxnSp>
+            <xdr:cxnSp macro="">
+              <xdr:nvCxnSpPr>
+                <xdr:cNvPr id="257" name="直線コネクタ 256">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DED6A5E-807A-B920-F54C-6D7ADB20E601}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvCxnSpPr/>
+              </xdr:nvCxnSpPr>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="3630426" y="2184454"/>
+                  <a:ext cx="0" cy="254849"/>
+                </a:xfrm>
+                <a:prstGeom prst="line">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln>
+                  <a:headEnd type="none" w="med" len="med"/>
+                  <a:tailEnd type="none" w="med" len="med"/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="1">
+                  <a:schemeClr val="dk1"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:schemeClr val="dk1"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:schemeClr val="dk1"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="tx1"/>
+                </a:fontRef>
+              </xdr:style>
+            </xdr:cxnSp>
+            <xdr:cxnSp macro="">
+              <xdr:nvCxnSpPr>
+                <xdr:cNvPr id="259" name="直線コネクタ 258">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1B61746-6154-AAED-9521-BBE3574FF526}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvCxnSpPr/>
+              </xdr:nvCxnSpPr>
+              <xdr:spPr>
+                <a:xfrm flipV="1">
+                  <a:off x="3122638" y="2183497"/>
+                  <a:ext cx="507789" cy="7327"/>
+                </a:xfrm>
+                <a:prstGeom prst="line">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln>
+                  <a:headEnd type="none" w="med" len="med"/>
+                  <a:tailEnd type="none" w="med" len="med"/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="1">
+                  <a:schemeClr val="dk1"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:schemeClr val="dk1"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:schemeClr val="dk1"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="tx1"/>
+                </a:fontRef>
+              </xdr:style>
+            </xdr:cxnSp>
+          </xdr:grpSp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="63" name="テキスト ボックス 62">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82DD9FA6-88C5-6F4C-8A4B-9E1BA55FE639}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="3267175" y="2150831"/>
+                <a:ext cx="933923" cy="318235"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
               <a:noFill/>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="ctr"/>
-              <a:r>
-                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-                <a:t>[</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-                <a:t>入力値 </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-                <a:t>= - or</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-                <a:t> 文字</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-                <a:t>]</a:t>
-              </a:r>
-              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:r>
+                  <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+                  <a:t>エラー文</a:t>
+                </a:r>
+                <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
       </xdr:grpSp>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="61" name="グループ化 60">
+          <xdr:cNvPr id="5" name="グループ化 4">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{625A996C-05FD-6A3E-F8A7-D541EA264A60}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B6E4646-AAE7-0444-B2E6-430ED2E2DF28}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10056,18 +10392,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="3137708" y="5418482"/>
-            <a:ext cx="1634318" cy="658468"/>
-            <a:chOff x="3078071" y="2333336"/>
-            <a:chExt cx="1638784" cy="664033"/>
+            <a:off x="3111617" y="6667501"/>
+            <a:ext cx="1212320" cy="489988"/>
+            <a:chOff x="3078071" y="2170044"/>
+            <a:chExt cx="1215633" cy="494129"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:grpSp>
           <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="62" name="グループ化 61">
+            <xdr:cNvPr id="6" name="グループ化 5">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D91CE40-2F1C-EE9A-EA78-E49A49794E8E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C0E526C-447D-C74A-01A6-1C69488DB405}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10083,10 +10419,10 @@
           </xdr:grpSpPr>
           <xdr:cxnSp macro="">
             <xdr:nvCxnSpPr>
-              <xdr:cNvPr id="256" name="直線矢印コネクタ 255">
+              <xdr:cNvPr id="11" name="直線矢印コネクタ 10">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4DC51FF-D4F2-3F45-5549-824C93C948F6}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42F0CDB3-3937-166C-B7AA-594672A8AD86}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -10127,10 +10463,10 @@
           </xdr:cxnSp>
           <xdr:cxnSp macro="">
             <xdr:nvCxnSpPr>
-              <xdr:cNvPr id="257" name="直線コネクタ 256">
+              <xdr:cNvPr id="18" name="直線コネクタ 17">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DED6A5E-807A-B920-F54C-6D7ADB20E601}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B343922E-3A8C-8DF6-9CB8-5778EE7C1334}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -10166,10 +10502,10 @@
           </xdr:cxnSp>
           <xdr:cxnSp macro="">
             <xdr:nvCxnSpPr>
-              <xdr:cNvPr id="259" name="直線コネクタ 258">
+              <xdr:cNvPr id="22" name="直線コネクタ 21">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1B61746-6154-AAED-9521-BBE3574FF526}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{351CD416-5886-0280-257C-C315BE7556AB}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -10206,10 +10542,10 @@
         </xdr:grpSp>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="63" name="テキスト ボックス 62">
+            <xdr:cNvPr id="10" name="テキスト ボックス 9">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82DD9FA6-88C5-6F4C-8A4B-9E1BA55FE639}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD770539-98AA-42B3-E1A6-CB589DE04C26}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10217,8 +10553,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3257624" y="2333336"/>
-              <a:ext cx="1459231" cy="664033"/>
+              <a:off x="3299791" y="2170044"/>
+              <a:ext cx="993913" cy="249721"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -10249,15 +10585,219 @@
               <a:pPr algn="ctr"/>
               <a:r>
                 <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-                <a:t>エラー文</a:t>
+                <a:t>入力受付中</a:t>
               </a:r>
-              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
             </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="24" name="グループ化 23">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29C6D27C-612A-B627-EED3-38F496FB105D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="3119900" y="5967620"/>
+            <a:ext cx="1484307" cy="492059"/>
+            <a:chOff x="3078071" y="2170044"/>
+            <a:chExt cx="1488363" cy="494129"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="26" name="グループ化 25">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{406376F2-8B9A-AA22-97BD-0437CF968C31}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="3078071" y="2407127"/>
+              <a:ext cx="519226" cy="257046"/>
+              <a:chOff x="3111201" y="2183497"/>
+              <a:chExt cx="519226" cy="257046"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:cxnSp macro="">
+            <xdr:nvCxnSpPr>
+              <xdr:cNvPr id="29" name="直線矢印コネクタ 28">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B29542D7-756B-7C70-133C-129A1A417D62}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvCxnSpPr/>
+            </xdr:nvCxnSpPr>
+            <xdr:spPr>
+              <a:xfrm flipH="1">
+                <a:off x="3111201" y="2440543"/>
+                <a:ext cx="518937" cy="0"/>
+              </a:xfrm>
+              <a:prstGeom prst="straightConnector1">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="dk1"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+                <a:round/>
+                <a:headEnd type="none" w="med" len="med"/>
+                <a:tailEnd type="triangle" w="med" len="med"/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="tx1"/>
+              </a:fontRef>
+            </xdr:style>
+          </xdr:cxnSp>
+          <xdr:cxnSp macro="">
+            <xdr:nvCxnSpPr>
+              <xdr:cNvPr id="31" name="直線コネクタ 30">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{092A6858-0FEF-BF2C-08A9-D7A075F010C1}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvCxnSpPr/>
+            </xdr:nvCxnSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="3630426" y="2184454"/>
+                <a:ext cx="0" cy="254849"/>
+              </a:xfrm>
+              <a:prstGeom prst="line">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:ln>
+                <a:headEnd type="none" w="med" len="med"/>
+                <a:tailEnd type="none" w="med" len="med"/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="1">
+                <a:schemeClr val="dk1"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:schemeClr val="dk1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="dk1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="tx1"/>
+              </a:fontRef>
+            </xdr:style>
+          </xdr:cxnSp>
+          <xdr:cxnSp macro="">
+            <xdr:nvCxnSpPr>
+              <xdr:cNvPr id="245" name="直線コネクタ 244">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D44DFD19-6F33-B6A0-9CB9-58102DA1039C}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvCxnSpPr/>
+            </xdr:nvCxnSpPr>
+            <xdr:spPr>
+              <a:xfrm flipV="1">
+                <a:off x="3122638" y="2183497"/>
+                <a:ext cx="507789" cy="7327"/>
+              </a:xfrm>
+              <a:prstGeom prst="line">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:ln>
+                <a:headEnd type="none" w="med" len="med"/>
+                <a:tailEnd type="none" w="med" len="med"/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="1">
+                <a:schemeClr val="dk1"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:schemeClr val="dk1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="dk1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="tx1"/>
+              </a:fontRef>
+            </xdr:style>
+          </xdr:cxnSp>
+        </xdr:grpSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="27" name="テキスト ボックス 26">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C62DE58-B96E-B114-F5C8-35D3C53D61EB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3152563" y="2170044"/>
+              <a:ext cx="1413871" cy="195985"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525" cmpd="sng">
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr"/>
               <a:r>
                 <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-                <a:t>選択肢表示に戻る</a:t>
+                <a:t>半径入力を要求</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
@@ -10268,23 +10808,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>157740</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>633677</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>28089</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>620243</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>217394</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="262" name="グループ化 261">
+        <xdr:cNvPr id="372" name="グループ化 371">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF6194E3-E944-FB89-FDB6-20898DCA8B8D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD9B3BE8-DA07-332E-01DC-86DE7F7F01D4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10292,18 +10832,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1438275" y="11606790"/>
-          <a:ext cx="4029075" cy="956685"/>
-          <a:chOff x="1447800" y="5186940"/>
-          <a:chExt cx="4029075" cy="956685"/>
+          <a:off x="1314034" y="13254232"/>
+          <a:ext cx="4068709" cy="2393662"/>
+          <a:chOff x="1377553" y="5057489"/>
+          <a:chExt cx="4099321" cy="2333911"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="263" name="グループ化 262">
+          <xdr:cNvPr id="373" name="グループ化 372">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE692418-C611-5B25-C9D3-D98310A39626}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{507E46DA-7759-30DC-3D09-4DD10D49B4F1}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10311,18 +10851,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="1447800" y="5186940"/>
-            <a:ext cx="4029075" cy="956685"/>
-            <a:chOff x="1581150" y="5148840"/>
-            <a:chExt cx="3905251" cy="956685"/>
+            <a:off x="1377553" y="5057489"/>
+            <a:ext cx="4099321" cy="2333911"/>
+            <a:chOff x="1377553" y="5057489"/>
+            <a:chExt cx="4099321" cy="2333911"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:grpSp>
           <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="80" name="グループ化 79">
+            <xdr:cNvPr id="386" name="グループ化 385">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E472489C-2A54-91DA-E225-29950C073D49}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E6DE536-D5E2-0500-B267-5664C41A48E7}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10330,18 +10870,18 @@
           </xdr:nvGrpSpPr>
           <xdr:grpSpPr>
             <a:xfrm>
-              <a:off x="1600201" y="5148840"/>
-              <a:ext cx="3886200" cy="956685"/>
-              <a:chOff x="559971" y="-278814"/>
-              <a:chExt cx="10999316" cy="13811251"/>
+              <a:off x="1377553" y="5057489"/>
+              <a:ext cx="4099321" cy="2333911"/>
+              <a:chOff x="313335" y="-2147646"/>
+              <a:chExt cx="11245952" cy="33693676"/>
             </a:xfrm>
           </xdr:grpSpPr>
           <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
-              <xdr:cNvPr id="82" name="正方形/長方形 81">
+              <xdr:cNvPr id="393" name="正方形/長方形 392">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F825957-2A7E-DBD4-6521-0D772E38F9CD}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10B015D3-3B25-9E91-F9C8-3273C4E9D6AB}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -10349,8 +10889,8 @@
             </xdr:nvSpPr>
             <xdr:spPr>
               <a:xfrm>
-                <a:off x="702080" y="-278814"/>
-                <a:ext cx="10857207" cy="13811251"/>
+                <a:off x="543046" y="-278814"/>
+                <a:ext cx="11016241" cy="31824844"/>
               </a:xfrm>
               <a:prstGeom prst="rect">
                 <a:avLst/>
@@ -10389,10 +10929,10 @@
           </xdr:sp>
           <xdr:grpSp>
             <xdr:nvGrpSpPr>
-              <xdr:cNvPr id="84" name="グループ化 83">
+              <xdr:cNvPr id="394" name="グループ化 393">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E324897F-6F0C-54BB-61A5-8363B4264154}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABB62352-B125-2D77-E42D-0D06AB593FEA}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -10400,18 +10940,18 @@
             </xdr:nvGrpSpPr>
             <xdr:grpSpPr>
               <a:xfrm>
-                <a:off x="559971" y="-218394"/>
-                <a:ext cx="2952991" cy="6875416"/>
-                <a:chOff x="-531643" y="-2361527"/>
-                <a:chExt cx="4429486" cy="6875430"/>
+                <a:off x="313335" y="-2147646"/>
+                <a:ext cx="4545567" cy="10881430"/>
+                <a:chOff x="-901595" y="-4290783"/>
+                <a:chExt cx="6818350" cy="10881452"/>
               </a:xfrm>
             </xdr:grpSpPr>
             <xdr:sp macro="" textlink="">
               <xdr:nvSpPr>
-                <xdr:cNvPr id="85" name="四角形: 1 つの角を切り取る 84">
+                <xdr:cNvPr id="395" name="四角形: 1 つの角を切り取る 394">
                   <a:extLst>
                     <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{866FA025-9698-CC1B-EDDB-13932556406F}"/>
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F579A2DC-CE30-14F7-0727-B270BA128225}"/>
                     </a:ext>
                   </a:extLst>
                 </xdr:cNvPr>
@@ -10419,12 +10959,12 @@
               </xdr:nvSpPr>
               <xdr:spPr>
                 <a:xfrm rot="10800000" flipH="1">
-                  <a:off x="-298957" y="-2361527"/>
-                  <a:ext cx="3983567" cy="6875430"/>
+                  <a:off x="-557030" y="-2361557"/>
+                  <a:ext cx="6196350" cy="7806644"/>
                 </a:xfrm>
                 <a:prstGeom prst="snip1Rect">
                   <a:avLst>
-                    <a:gd name="adj" fmla="val 27778"/>
+                    <a:gd name="adj" fmla="val 21489"/>
                   </a:avLst>
                 </a:prstGeom>
                 <a:solidFill>
@@ -10467,10 +11007,10 @@
             </xdr:sp>
             <xdr:sp macro="" textlink="">
               <xdr:nvSpPr>
-                <xdr:cNvPr id="89" name="正方形/長方形 88">
+                <xdr:cNvPr id="396" name="正方形/長方形 395">
                   <a:extLst>
                     <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1320583-1F81-77F2-E5AE-E78C79EB7879}"/>
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80D4CC4B-4B00-0EAB-1947-DAD1B6A3639D}"/>
                     </a:ext>
                   </a:extLst>
                 </xdr:cNvPr>
@@ -10478,8 +11018,8 @@
               </xdr:nvSpPr>
               <xdr:spPr>
                 <a:xfrm rot="10800000" flipV="1">
-                  <a:off x="-531643" y="-1017884"/>
-                  <a:ext cx="4429486" cy="3677391"/>
+                  <a:off x="-901595" y="-4290783"/>
+                  <a:ext cx="6818350" cy="10881452"/>
                 </a:xfrm>
                 <a:prstGeom prst="rect">
                   <a:avLst/>
@@ -10516,7 +11056,18 @@
                         <a:sysClr val="windowText" lastClr="000000"/>
                       </a:solidFill>
                     </a:rPr>
-                    <a:t>alt </a:t>
+                    <a:t>loop</a:t>
+                  </a:r>
+                </a:p>
+                <a:p>
+                  <a:pPr algn="ctr"/>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>[</a:t>
                   </a:r>
                   <a:r>
                     <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
@@ -10524,87 +11075,262 @@
                         <a:sysClr val="windowText" lastClr="000000"/>
                       </a:solidFill>
                     </a:rPr>
-                    <a:t>入力値</a:t>
+                    <a:t>入力値 </a:t>
                   </a:r>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>= - or </a:t>
+                  </a:r>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>文字</a:t>
+                  </a:r>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>]</a:t>
+                  </a:r>
+                  <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:endParaRPr>
                 </a:p>
               </xdr:txBody>
             </xdr:sp>
           </xdr:grpSp>
         </xdr:grpSp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="81" name="テキスト ボックス 80">
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="387" name="グループ化 386">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{853847A4-3F72-F05F-856C-1E91F87C83F0}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92702D74-235B-A1F2-6C3A-37562DE494C3}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
             <a:xfrm>
-              <a:off x="1581150" y="5734050"/>
-              <a:ext cx="1476375" cy="247650"/>
+              <a:off x="3137709" y="5237503"/>
+              <a:ext cx="1119967" cy="509039"/>
+              <a:chOff x="3078071" y="2150831"/>
+              <a:chExt cx="1123027" cy="513342"/>
             </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="9525" cmpd="sng">
+          </xdr:grpSpPr>
+          <xdr:grpSp>
+            <xdr:nvGrpSpPr>
+              <xdr:cNvPr id="388" name="グループ化 387">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{077969A7-2567-DBC0-E5EF-61AFDAB0F75B}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvGrpSpPr/>
+            </xdr:nvGrpSpPr>
+            <xdr:grpSpPr>
+              <a:xfrm>
+                <a:off x="3078071" y="2407127"/>
+                <a:ext cx="519226" cy="257046"/>
+                <a:chOff x="3111201" y="2183497"/>
+                <a:chExt cx="519226" cy="257046"/>
+              </a:xfrm>
+            </xdr:grpSpPr>
+            <xdr:cxnSp macro="">
+              <xdr:nvCxnSpPr>
+                <xdr:cNvPr id="390" name="直線矢印コネクタ 389">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B296186-71D2-99B2-F3AF-9809F21FD6CF}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvCxnSpPr/>
+              </xdr:nvCxnSpPr>
+              <xdr:spPr>
+                <a:xfrm flipH="1">
+                  <a:off x="3111201" y="2440543"/>
+                  <a:ext cx="518937" cy="0"/>
+                </a:xfrm>
+                <a:prstGeom prst="straightConnector1">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                  <a:round/>
+                  <a:headEnd type="none" w="med" len="med"/>
+                  <a:tailEnd type="triangle" w="med" len="med"/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="tx1"/>
+                </a:fontRef>
+              </xdr:style>
+            </xdr:cxnSp>
+            <xdr:cxnSp macro="">
+              <xdr:nvCxnSpPr>
+                <xdr:cNvPr id="391" name="直線コネクタ 390">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8715CCB-49AA-1808-6D39-6FBDA39C6B2F}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvCxnSpPr/>
+              </xdr:nvCxnSpPr>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="3630426" y="2184454"/>
+                  <a:ext cx="0" cy="254849"/>
+                </a:xfrm>
+                <a:prstGeom prst="line">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln>
+                  <a:headEnd type="none" w="med" len="med"/>
+                  <a:tailEnd type="none" w="med" len="med"/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="1">
+                  <a:schemeClr val="dk1"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:schemeClr val="dk1"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:schemeClr val="dk1"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="tx1"/>
+                </a:fontRef>
+              </xdr:style>
+            </xdr:cxnSp>
+            <xdr:cxnSp macro="">
+              <xdr:nvCxnSpPr>
+                <xdr:cNvPr id="392" name="直線コネクタ 391">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9C9DCAF-88E5-6287-2E15-9F0DE62C0E33}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvCxnSpPr/>
+              </xdr:nvCxnSpPr>
+              <xdr:spPr>
+                <a:xfrm flipV="1">
+                  <a:off x="3122638" y="2183497"/>
+                  <a:ext cx="507789" cy="7327"/>
+                </a:xfrm>
+                <a:prstGeom prst="line">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln>
+                  <a:headEnd type="none" w="med" len="med"/>
+                  <a:tailEnd type="none" w="med" len="med"/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="1">
+                  <a:schemeClr val="dk1"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:schemeClr val="dk1"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:schemeClr val="dk1"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="tx1"/>
+                </a:fontRef>
+              </xdr:style>
+            </xdr:cxnSp>
+          </xdr:grpSp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="389" name="テキスト ボックス 388">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE2B93FD-D17A-F5C7-E6C1-1F42670E0BA2}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="3267175" y="2150831"/>
+                <a:ext cx="933923" cy="318235"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
               <a:noFill/>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="ctr"/>
-              <a:r>
-                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-                <a:t>[</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-                <a:t>入力値 </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-                <a:t>= - or</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-                <a:t> 文字</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-                <a:t>]</a:t>
-              </a:r>
-              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:r>
+                  <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+                  <a:t>エラー文</a:t>
+                </a:r>
+                <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
       </xdr:grpSp>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="264" name="グループ化 263">
+          <xdr:cNvPr id="374" name="グループ化 373">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5E1981C-2964-5F7E-4201-1EC8824FE124}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42FF5CDA-91E3-E34C-9B74-BBFFE3537E33}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10612,18 +11338,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="3137708" y="5418482"/>
-            <a:ext cx="1634318" cy="658468"/>
-            <a:chOff x="3078071" y="2333336"/>
-            <a:chExt cx="1638784" cy="664033"/>
+            <a:off x="3138673" y="6667501"/>
+            <a:ext cx="1185263" cy="489988"/>
+            <a:chOff x="3105202" y="2170044"/>
+            <a:chExt cx="1188502" cy="494129"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:grpSp>
           <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="265" name="グループ化 264">
+            <xdr:cNvPr id="381" name="グループ化 380">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{109555CC-58FF-9E3C-0AAB-05EBEA737A6C}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E84193C-DAC9-C3AA-43BD-F34FC4896F2A}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10631,27 +11357,27 @@
           </xdr:nvGrpSpPr>
           <xdr:grpSpPr>
             <a:xfrm>
-              <a:off x="3078071" y="2407127"/>
-              <a:ext cx="519226" cy="257046"/>
-              <a:chOff x="3111201" y="2183497"/>
-              <a:chExt cx="519226" cy="257046"/>
+              <a:off x="3105202" y="2407127"/>
+              <a:ext cx="492095" cy="257046"/>
+              <a:chOff x="3138332" y="2183497"/>
+              <a:chExt cx="492095" cy="257046"/>
             </a:xfrm>
           </xdr:grpSpPr>
           <xdr:cxnSp macro="">
             <xdr:nvCxnSpPr>
-              <xdr:cNvPr id="77" name="直線矢印コネクタ 76">
+              <xdr:cNvPr id="383" name="直線矢印コネクタ 382">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40D130BB-D411-B09D-79A0-AB8D4DC52F76}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8814247B-D9CE-E561-EB20-46350B205523}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
               <xdr:cNvCxnSpPr/>
             </xdr:nvCxnSpPr>
             <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="3111201" y="2440543"/>
-                <a:ext cx="518937" cy="0"/>
+              <a:xfrm flipH="1" flipV="1">
+                <a:off x="3138332" y="2438246"/>
+                <a:ext cx="491805" cy="2297"/>
               </a:xfrm>
               <a:prstGeom prst="straightConnector1">
                 <a:avLst/>
@@ -10683,10 +11409,10 @@
           </xdr:cxnSp>
           <xdr:cxnSp macro="">
             <xdr:nvCxnSpPr>
-              <xdr:cNvPr id="78" name="直線コネクタ 77">
+              <xdr:cNvPr id="384" name="直線コネクタ 383">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3617E612-D0EC-A805-48EA-70D6056C43B8}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F0E6CFB-7EBA-325F-C0A0-E78BFACDBF0A}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -10722,10 +11448,10 @@
           </xdr:cxnSp>
           <xdr:cxnSp macro="">
             <xdr:nvCxnSpPr>
-              <xdr:cNvPr id="79" name="直線コネクタ 78">
+              <xdr:cNvPr id="385" name="直線コネクタ 384">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F12DAF96-717C-4727-5221-FC7BA3B9302E}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BEB0605-E7BA-E473-4F2C-31ABBDB100D8}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -10733,8 +11459,8 @@
             </xdr:nvCxnSpPr>
             <xdr:spPr>
               <a:xfrm flipV="1">
-                <a:off x="3122638" y="2183497"/>
-                <a:ext cx="507789" cy="7327"/>
+                <a:off x="3152956" y="2183497"/>
+                <a:ext cx="477471" cy="6874"/>
               </a:xfrm>
               <a:prstGeom prst="line">
                 <a:avLst/>
@@ -10762,10 +11488,10 @@
         </xdr:grpSp>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="76" name="テキスト ボックス 75">
+            <xdr:cNvPr id="382" name="テキスト ボックス 381">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7770FF8-3105-5D87-841F-378115F046E5}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E32FAAC2-19B5-032B-E8BE-6E6FEE0F77CE}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10773,8 +11499,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3257624" y="2333336"/>
-              <a:ext cx="1459231" cy="664033"/>
+              <a:off x="3299791" y="2170044"/>
+              <a:ext cx="993913" cy="249721"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -10805,42 +11531,176 @@
               <a:pPr algn="ctr"/>
               <a:r>
                 <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-                <a:t>エラー文</a:t>
-              </a:r>
-              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-            </a:p>
-            <a:p>
-              <a:pPr algn="ctr"/>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-                <a:t>選択肢表示に戻る</a:t>
+                <a:t>入力受付中</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="376" name="グループ化 375">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE786A3E-0CFE-0675-1CA9-2C13104BE9DC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="3131305" y="6203708"/>
+            <a:ext cx="506405" cy="255969"/>
+            <a:chOff x="3122638" y="2183497"/>
+            <a:chExt cx="507789" cy="257046"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="378" name="直線矢印コネクタ 377">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A70469B9-4321-22BA-2BDC-C0B89763C454}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1" flipV="1">
+              <a:off x="3151961" y="2434804"/>
+              <a:ext cx="478176" cy="5739"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+              <a:headEnd type="none" w="med" len="med"/>
+              <a:tailEnd type="triangle" w="med" len="med"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="379" name="直線コネクタ 378">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D63368B-12E9-EFFA-5203-4DD0D4AD3D63}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3630426" y="2184454"/>
+              <a:ext cx="0" cy="254849"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:headEnd type="none" w="med" len="med"/>
+              <a:tailEnd type="none" w="med" len="med"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="380" name="直線コネクタ 379">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F70C04DB-381B-19EF-8F83-451BFC272D48}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipV="1">
+              <a:off x="3122638" y="2183497"/>
+              <a:ext cx="507789" cy="7327"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:headEnd type="none" w="med" len="med"/>
+              <a:tailEnd type="none" w="med" len="med"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
       </xdr:grpSp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>157740</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>644883</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>28089</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>631449</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>217394</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="90" name="グループ化 89">
+        <xdr:cNvPr id="401" name="グループ化 400">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{253662E8-A766-61B2-B561-8704BDA8EC24}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF02C24D-08A6-3BB3-E325-AC65E673A241}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10848,18 +11708,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1447800" y="13988040"/>
-          <a:ext cx="4029075" cy="956685"/>
-          <a:chOff x="1447800" y="5186940"/>
-          <a:chExt cx="4029075" cy="956685"/>
+          <a:off x="1325240" y="17173089"/>
+          <a:ext cx="4068709" cy="2393662"/>
+          <a:chOff x="1377553" y="5057489"/>
+          <a:chExt cx="4099321" cy="2333911"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="93" name="グループ化 92">
+          <xdr:cNvPr id="402" name="グループ化 401">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18F450FF-96BE-8472-659F-7A05A6B94562}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2193946-C59E-D41E-CAEE-1E3E42E46475}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -10867,18 +11727,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="1447800" y="5186940"/>
-            <a:ext cx="4029075" cy="956685"/>
-            <a:chOff x="1581150" y="5148840"/>
-            <a:chExt cx="3905251" cy="956685"/>
+            <a:off x="1377553" y="5057489"/>
+            <a:ext cx="4099321" cy="2333911"/>
+            <a:chOff x="1377553" y="5057489"/>
+            <a:chExt cx="4099321" cy="2333911"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:grpSp>
           <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="350" name="グループ化 349">
+            <xdr:cNvPr id="413" name="グループ化 412">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F67C7D92-020B-5E9F-F617-DEAACD0CBD67}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{071C573D-7855-EB7B-9285-218E7662BCDB}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -10886,18 +11746,18 @@
           </xdr:nvGrpSpPr>
           <xdr:grpSpPr>
             <a:xfrm>
-              <a:off x="1600201" y="5148840"/>
-              <a:ext cx="3886200" cy="956685"/>
-              <a:chOff x="559971" y="-278814"/>
-              <a:chExt cx="10999316" cy="13811251"/>
+              <a:off x="1377553" y="5057489"/>
+              <a:ext cx="4099321" cy="2333911"/>
+              <a:chOff x="313335" y="-2147646"/>
+              <a:chExt cx="11245952" cy="33693676"/>
             </a:xfrm>
           </xdr:grpSpPr>
           <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
-              <xdr:cNvPr id="96" name="正方形/長方形 95">
+              <xdr:cNvPr id="420" name="正方形/長方形 419">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDE94364-F8C6-A3F3-BE1D-7A7F47277683}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F70F091-F03B-B5D7-955D-300F9D58AD5C}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -10905,8 +11765,8 @@
             </xdr:nvSpPr>
             <xdr:spPr>
               <a:xfrm>
-                <a:off x="702080" y="-278814"/>
-                <a:ext cx="10857207" cy="13811251"/>
+                <a:off x="543046" y="-278814"/>
+                <a:ext cx="11016241" cy="31824844"/>
               </a:xfrm>
               <a:prstGeom prst="rect">
                 <a:avLst/>
@@ -10945,10 +11805,10 @@
           </xdr:sp>
           <xdr:grpSp>
             <xdr:nvGrpSpPr>
-              <xdr:cNvPr id="97" name="グループ化 96">
+              <xdr:cNvPr id="421" name="グループ化 420">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06AADDFC-3641-3206-53E4-0EC876209A9F}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEA88998-E424-4858-A82F-6B95AFFA8FB4}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -10956,18 +11816,18 @@
             </xdr:nvGrpSpPr>
             <xdr:grpSpPr>
               <a:xfrm>
-                <a:off x="559971" y="-218394"/>
-                <a:ext cx="2952991" cy="6875416"/>
-                <a:chOff x="-531643" y="-2361527"/>
-                <a:chExt cx="4429486" cy="6875430"/>
+                <a:off x="313335" y="-2147646"/>
+                <a:ext cx="4545567" cy="10881430"/>
+                <a:chOff x="-901595" y="-4290783"/>
+                <a:chExt cx="6818350" cy="10881452"/>
               </a:xfrm>
             </xdr:grpSpPr>
             <xdr:sp macro="" textlink="">
               <xdr:nvSpPr>
-                <xdr:cNvPr id="98" name="四角形: 1 つの角を切り取る 97">
+                <xdr:cNvPr id="422" name="四角形: 1 つの角を切り取る 421">
                   <a:extLst>
                     <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DFB9311-F5BC-391D-30CC-D5006183A0C1}"/>
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B36D871-5C6E-ADD6-5FD0-D6ED3A1D5353}"/>
                     </a:ext>
                   </a:extLst>
                 </xdr:cNvPr>
@@ -10975,12 +11835,12 @@
               </xdr:nvSpPr>
               <xdr:spPr>
                 <a:xfrm rot="10800000" flipH="1">
-                  <a:off x="-298957" y="-2361527"/>
-                  <a:ext cx="3983567" cy="6875430"/>
+                  <a:off x="-557030" y="-2361557"/>
+                  <a:ext cx="6196350" cy="7806644"/>
                 </a:xfrm>
                 <a:prstGeom prst="snip1Rect">
                   <a:avLst>
-                    <a:gd name="adj" fmla="val 27778"/>
+                    <a:gd name="adj" fmla="val 21489"/>
                   </a:avLst>
                 </a:prstGeom>
                 <a:solidFill>
@@ -11023,10 +11883,10 @@
             </xdr:sp>
             <xdr:sp macro="" textlink="">
               <xdr:nvSpPr>
-                <xdr:cNvPr id="99" name="正方形/長方形 98">
+                <xdr:cNvPr id="423" name="正方形/長方形 422">
                   <a:extLst>
                     <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA0C0BD2-4168-E16F-3E6D-A43AB2B58282}"/>
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F2E8B9B-E552-F933-A28A-82947BE22299}"/>
                     </a:ext>
                   </a:extLst>
                 </xdr:cNvPr>
@@ -11034,8 +11894,8 @@
               </xdr:nvSpPr>
               <xdr:spPr>
                 <a:xfrm rot="10800000" flipV="1">
-                  <a:off x="-531643" y="-1017884"/>
-                  <a:ext cx="4429486" cy="3677391"/>
+                  <a:off x="-901595" y="-4290783"/>
+                  <a:ext cx="6818350" cy="10881452"/>
                 </a:xfrm>
                 <a:prstGeom prst="rect">
                   <a:avLst/>
@@ -11072,7 +11932,18 @@
                         <a:sysClr val="windowText" lastClr="000000"/>
                       </a:solidFill>
                     </a:rPr>
-                    <a:t>alt </a:t>
+                    <a:t>loop</a:t>
+                  </a:r>
+                </a:p>
+                <a:p>
+                  <a:pPr algn="ctr"/>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>[</a:t>
                   </a:r>
                   <a:r>
                     <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
@@ -11080,87 +11951,262 @@
                         <a:sysClr val="windowText" lastClr="000000"/>
                       </a:solidFill>
                     </a:rPr>
-                    <a:t>入力値</a:t>
+                    <a:t>入力値 </a:t>
                   </a:r>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>= - or </a:t>
+                  </a:r>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>文字</a:t>
+                  </a:r>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>]</a:t>
+                  </a:r>
+                  <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:endParaRPr>
                 </a:p>
               </xdr:txBody>
             </xdr:sp>
           </xdr:grpSp>
         </xdr:grpSp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="351" name="テキスト ボックス 350">
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="414" name="グループ化 413">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23C934EE-3F80-0A9A-1712-638B322CB206}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EED3F7D0-2DC8-79ED-0687-CD96CE9E9AD2}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
             <a:xfrm>
-              <a:off x="1581150" y="5734050"/>
-              <a:ext cx="1476375" cy="247650"/>
+              <a:off x="3137709" y="5237503"/>
+              <a:ext cx="1119967" cy="509039"/>
+              <a:chOff x="3078071" y="2150831"/>
+              <a:chExt cx="1123027" cy="513342"/>
             </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="9525" cmpd="sng">
+          </xdr:grpSpPr>
+          <xdr:grpSp>
+            <xdr:nvGrpSpPr>
+              <xdr:cNvPr id="415" name="グループ化 414">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EF24AE0-8C57-82CB-B1D6-398EA871F8FB}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvGrpSpPr/>
+            </xdr:nvGrpSpPr>
+            <xdr:grpSpPr>
+              <a:xfrm>
+                <a:off x="3078071" y="2407127"/>
+                <a:ext cx="519226" cy="257046"/>
+                <a:chOff x="3111201" y="2183497"/>
+                <a:chExt cx="519226" cy="257046"/>
+              </a:xfrm>
+            </xdr:grpSpPr>
+            <xdr:cxnSp macro="">
+              <xdr:nvCxnSpPr>
+                <xdr:cNvPr id="417" name="直線矢印コネクタ 416">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B5E72AD-1923-7B25-C3EC-1259BC8DC2DA}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvCxnSpPr/>
+              </xdr:nvCxnSpPr>
+              <xdr:spPr>
+                <a:xfrm flipH="1">
+                  <a:off x="3111201" y="2440543"/>
+                  <a:ext cx="518937" cy="0"/>
+                </a:xfrm>
+                <a:prstGeom prst="straightConnector1">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                  <a:round/>
+                  <a:headEnd type="none" w="med" len="med"/>
+                  <a:tailEnd type="triangle" w="med" len="med"/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="tx1"/>
+                </a:fontRef>
+              </xdr:style>
+            </xdr:cxnSp>
+            <xdr:cxnSp macro="">
+              <xdr:nvCxnSpPr>
+                <xdr:cNvPr id="418" name="直線コネクタ 417">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2C7D1CC-B614-2BD7-88ED-80C8ED294C05}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvCxnSpPr/>
+              </xdr:nvCxnSpPr>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="3630426" y="2184454"/>
+                  <a:ext cx="0" cy="254849"/>
+                </a:xfrm>
+                <a:prstGeom prst="line">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln>
+                  <a:headEnd type="none" w="med" len="med"/>
+                  <a:tailEnd type="none" w="med" len="med"/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="1">
+                  <a:schemeClr val="dk1"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:schemeClr val="dk1"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:schemeClr val="dk1"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="tx1"/>
+                </a:fontRef>
+              </xdr:style>
+            </xdr:cxnSp>
+            <xdr:cxnSp macro="">
+              <xdr:nvCxnSpPr>
+                <xdr:cNvPr id="419" name="直線コネクタ 418">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2724603C-8E91-0D06-A68C-882AFC798F6C}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvCxnSpPr/>
+              </xdr:nvCxnSpPr>
+              <xdr:spPr>
+                <a:xfrm flipV="1">
+                  <a:off x="3122638" y="2183497"/>
+                  <a:ext cx="507789" cy="7327"/>
+                </a:xfrm>
+                <a:prstGeom prst="line">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln>
+                  <a:headEnd type="none" w="med" len="med"/>
+                  <a:tailEnd type="none" w="med" len="med"/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="1">
+                  <a:schemeClr val="dk1"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:schemeClr val="dk1"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:schemeClr val="dk1"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="tx1"/>
+                </a:fontRef>
+              </xdr:style>
+            </xdr:cxnSp>
+          </xdr:grpSp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="416" name="テキスト ボックス 415">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BD9D233-6B7D-3D56-F52C-A902245DCDCC}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="3267175" y="2150831"/>
+                <a:ext cx="933923" cy="318235"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
               <a:noFill/>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="ctr"/>
-              <a:r>
-                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-                <a:t>[</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-                <a:t>入力値 </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-                <a:t>= - or</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-                <a:t> 文字</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-                <a:t>]</a:t>
-              </a:r>
-              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:r>
+                  <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+                  <a:t>エラー文</a:t>
+                </a:r>
+                <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
       </xdr:grpSp>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="94" name="グループ化 93">
+          <xdr:cNvPr id="403" name="グループ化 402">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E06E738-93A0-7C15-073A-10839B6F160D}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4CA7BA1-308D-E488-085B-4E6BEC30309D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11168,18 +12214,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="3137708" y="5418482"/>
-            <a:ext cx="1634318" cy="658468"/>
-            <a:chOff x="3078071" y="2333336"/>
-            <a:chExt cx="1638784" cy="664033"/>
+            <a:off x="3138673" y="6667501"/>
+            <a:ext cx="1185263" cy="489988"/>
+            <a:chOff x="3105202" y="2170044"/>
+            <a:chExt cx="1188502" cy="494129"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:grpSp>
           <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="95" name="グループ化 94">
+            <xdr:cNvPr id="408" name="グループ化 407">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C76B0B01-E25B-A699-4004-A7D8517F5A8A}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6563052B-4ED2-B301-D813-8CAD83D6FC53}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11187,27 +12233,27 @@
           </xdr:nvGrpSpPr>
           <xdr:grpSpPr>
             <a:xfrm>
-              <a:off x="3078071" y="2407127"/>
-              <a:ext cx="519226" cy="257046"/>
-              <a:chOff x="3111201" y="2183497"/>
-              <a:chExt cx="519226" cy="257046"/>
+              <a:off x="3105202" y="2407127"/>
+              <a:ext cx="492095" cy="257046"/>
+              <a:chOff x="3138332" y="2183497"/>
+              <a:chExt cx="492095" cy="257046"/>
             </a:xfrm>
           </xdr:grpSpPr>
           <xdr:cxnSp macro="">
             <xdr:nvCxnSpPr>
-              <xdr:cNvPr id="292" name="直線矢印コネクタ 291">
+              <xdr:cNvPr id="410" name="直線矢印コネクタ 409">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C15D7DF8-CF32-5BBB-9950-EB0687AC2FC4}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0683ECA1-9F8B-FAC7-84A0-EEEB47AB7A67}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
               <xdr:cNvCxnSpPr/>
             </xdr:nvCxnSpPr>
             <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="3111201" y="2440543"/>
-                <a:ext cx="518937" cy="0"/>
+              <a:xfrm flipH="1" flipV="1">
+                <a:off x="3138332" y="2438246"/>
+                <a:ext cx="491805" cy="2297"/>
               </a:xfrm>
               <a:prstGeom prst="straightConnector1">
                 <a:avLst/>
@@ -11239,10 +12285,10 @@
           </xdr:cxnSp>
           <xdr:cxnSp macro="">
             <xdr:nvCxnSpPr>
-              <xdr:cNvPr id="348" name="直線コネクタ 347">
+              <xdr:cNvPr id="411" name="直線コネクタ 410">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11DC60C6-0CA9-4D02-EE1F-1902A52A5A43}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E43A7136-4952-3D90-731A-A26C5F82AB20}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -11278,10 +12324,10 @@
           </xdr:cxnSp>
           <xdr:cxnSp macro="">
             <xdr:nvCxnSpPr>
-              <xdr:cNvPr id="349" name="直線コネクタ 348">
+              <xdr:cNvPr id="412" name="直線コネクタ 411">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67BADC01-0A6A-FA9E-A0BA-09D6ABDACA9C}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67EBA527-1814-0542-69E6-9863CEA9B812}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -11289,8 +12335,8 @@
             </xdr:nvCxnSpPr>
             <xdr:spPr>
               <a:xfrm flipV="1">
-                <a:off x="3122638" y="2183497"/>
-                <a:ext cx="507789" cy="7327"/>
+                <a:off x="3152956" y="2183497"/>
+                <a:ext cx="477471" cy="6874"/>
               </a:xfrm>
               <a:prstGeom prst="line">
                 <a:avLst/>
@@ -11318,10 +12364,10 @@
         </xdr:grpSp>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="288" name="テキスト ボックス 287">
+            <xdr:cNvPr id="409" name="テキスト ボックス 408">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFBD957A-7677-50D9-D956-3D097E737FFF}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{538DA60F-C6BB-D6EB-FBB2-B4AF16EB1640}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11329,8 +12375,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3257624" y="2333336"/>
-              <a:ext cx="1459231" cy="664033"/>
+              <a:off x="3299791" y="2170044"/>
+              <a:ext cx="993913" cy="249721"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -11361,42 +12407,176 @@
               <a:pPr algn="ctr"/>
               <a:r>
                 <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-                <a:t>エラー文</a:t>
-              </a:r>
-              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-            </a:p>
-            <a:p>
-              <a:pPr algn="ctr"/>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-                <a:t>選択肢表示に戻る</a:t>
+                <a:t>入力受付中</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="404" name="グループ化 403">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E5B7FE9-D3FB-76AE-E303-15BC5C71941E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="3131305" y="6203708"/>
+            <a:ext cx="506405" cy="255969"/>
+            <a:chOff x="3122638" y="2183497"/>
+            <a:chExt cx="507789" cy="257046"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="405" name="直線矢印コネクタ 404">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{390A92B8-F821-4078-37DD-AAF65E35F5C5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1" flipV="1">
+              <a:off x="3142522" y="2439902"/>
+              <a:ext cx="487615" cy="641"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+              <a:headEnd type="none" w="med" len="med"/>
+              <a:tailEnd type="triangle" w="med" len="med"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="406" name="直線コネクタ 405">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37E5A9E3-B556-71EF-011E-F59B2C559430}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3630426" y="2184454"/>
+              <a:ext cx="0" cy="254849"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:headEnd type="none" w="med" len="med"/>
+              <a:tailEnd type="none" w="med" len="med"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="407" name="直線コネクタ 406">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6643D4EC-FAF8-2B20-5C80-0A9678FF52D6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipV="1">
+              <a:off x="3122638" y="2183497"/>
+              <a:ext cx="507789" cy="7327"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:headEnd type="none" w="med" len="med"/>
+              <a:tailEnd type="none" w="med" len="med"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
       </xdr:grpSp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>157740</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>644884</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>41695</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:colOff>631450</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>231000</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="100" name="グループ化 99">
+        <xdr:cNvPr id="425" name="グループ化 424">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C27F326E-85D9-3AE5-6FD4-D0718A16DA10}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB6CD94F-2074-406E-10E9-94F52D29DA3D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11404,18 +12584,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1438275" y="19941165"/>
-          <a:ext cx="4029075" cy="956685"/>
-          <a:chOff x="1447800" y="5186940"/>
-          <a:chExt cx="4029075" cy="956685"/>
+          <a:off x="1325241" y="24779481"/>
+          <a:ext cx="4068709" cy="2393662"/>
+          <a:chOff x="1377553" y="5057489"/>
+          <a:chExt cx="4099321" cy="2333911"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="102" name="グループ化 101">
+          <xdr:cNvPr id="426" name="グループ化 425">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFF443CA-A46B-D40C-D050-54BA73D14AD4}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9DD5BF0-EFAD-856C-B8A7-69121A3BC979}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11423,18 +12603,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="1447800" y="5186940"/>
-            <a:ext cx="4029075" cy="956685"/>
-            <a:chOff x="1581150" y="5148840"/>
-            <a:chExt cx="3905251" cy="956685"/>
+            <a:off x="1377553" y="5057489"/>
+            <a:ext cx="4099321" cy="2333911"/>
+            <a:chOff x="1377553" y="5057489"/>
+            <a:chExt cx="4099321" cy="2333911"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:grpSp>
           <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="109" name="グループ化 108">
+            <xdr:cNvPr id="437" name="グループ化 436">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89155867-CFB1-AAE5-BF9C-C80DA8A3C9BB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3322012F-0A41-12F6-54A6-09BF30B3DDFA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11442,18 +12622,18 @@
           </xdr:nvGrpSpPr>
           <xdr:grpSpPr>
             <a:xfrm>
-              <a:off x="1600201" y="5148840"/>
-              <a:ext cx="3886200" cy="956685"/>
-              <a:chOff x="559971" y="-278814"/>
-              <a:chExt cx="10999316" cy="13811251"/>
+              <a:off x="1377553" y="5057489"/>
+              <a:ext cx="4099321" cy="2333911"/>
+              <a:chOff x="313335" y="-2147646"/>
+              <a:chExt cx="11245952" cy="33693676"/>
             </a:xfrm>
           </xdr:grpSpPr>
           <xdr:sp macro="" textlink="">
             <xdr:nvSpPr>
-              <xdr:cNvPr id="111" name="正方形/長方形 110">
+              <xdr:cNvPr id="444" name="正方形/長方形 443">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C448D927-3869-00CF-0C7F-CA4580FE2CBC}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66F4C011-F253-5711-D85A-495CB336E0A9}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -11461,8 +12641,8 @@
             </xdr:nvSpPr>
             <xdr:spPr>
               <a:xfrm>
-                <a:off x="702080" y="-278814"/>
-                <a:ext cx="10857207" cy="13811251"/>
+                <a:off x="543046" y="-278814"/>
+                <a:ext cx="11016241" cy="31824844"/>
               </a:xfrm>
               <a:prstGeom prst="rect">
                 <a:avLst/>
@@ -11501,10 +12681,10 @@
           </xdr:sp>
           <xdr:grpSp>
             <xdr:nvGrpSpPr>
-              <xdr:cNvPr id="112" name="グループ化 111">
+              <xdr:cNvPr id="445" name="グループ化 444">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBBD35C7-BE3B-CB8E-6102-7B1F7A7153C2}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{306E2BD7-0A70-A07B-F5EE-D0D75EC73254}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -11512,18 +12692,18 @@
             </xdr:nvGrpSpPr>
             <xdr:grpSpPr>
               <a:xfrm>
-                <a:off x="559971" y="-218394"/>
-                <a:ext cx="2952991" cy="6875416"/>
-                <a:chOff x="-531643" y="-2361527"/>
-                <a:chExt cx="4429486" cy="6875430"/>
+                <a:off x="313335" y="-2147646"/>
+                <a:ext cx="4545567" cy="10881430"/>
+                <a:chOff x="-901595" y="-4290783"/>
+                <a:chExt cx="6818350" cy="10881452"/>
               </a:xfrm>
             </xdr:grpSpPr>
             <xdr:sp macro="" textlink="">
               <xdr:nvSpPr>
-                <xdr:cNvPr id="113" name="四角形: 1 つの角を切り取る 112">
+                <xdr:cNvPr id="446" name="四角形: 1 つの角を切り取る 445">
                   <a:extLst>
                     <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAB3255F-D01D-471F-4119-5CB994ACB377}"/>
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C7CE32E-E18F-6496-D3BB-5AC642D29898}"/>
                     </a:ext>
                   </a:extLst>
                 </xdr:cNvPr>
@@ -11531,12 +12711,12 @@
               </xdr:nvSpPr>
               <xdr:spPr>
                 <a:xfrm rot="10800000" flipH="1">
-                  <a:off x="-298957" y="-2361527"/>
-                  <a:ext cx="3983567" cy="6875430"/>
+                  <a:off x="-557030" y="-2361557"/>
+                  <a:ext cx="6196350" cy="7806644"/>
                 </a:xfrm>
                 <a:prstGeom prst="snip1Rect">
                   <a:avLst>
-                    <a:gd name="adj" fmla="val 27778"/>
+                    <a:gd name="adj" fmla="val 21489"/>
                   </a:avLst>
                 </a:prstGeom>
                 <a:solidFill>
@@ -11579,10 +12759,10 @@
             </xdr:sp>
             <xdr:sp macro="" textlink="">
               <xdr:nvSpPr>
-                <xdr:cNvPr id="114" name="正方形/長方形 113">
+                <xdr:cNvPr id="447" name="正方形/長方形 446">
                   <a:extLst>
                     <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1B54024-DE5F-9283-2697-0024A1011386}"/>
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24F380C5-6BCF-686A-55CA-C42739D5DF5D}"/>
                     </a:ext>
                   </a:extLst>
                 </xdr:cNvPr>
@@ -11590,8 +12770,8 @@
               </xdr:nvSpPr>
               <xdr:spPr>
                 <a:xfrm rot="10800000" flipV="1">
-                  <a:off x="-531643" y="-1017884"/>
-                  <a:ext cx="4429486" cy="3677391"/>
+                  <a:off x="-901595" y="-4290783"/>
+                  <a:ext cx="6818350" cy="10881452"/>
                 </a:xfrm>
                 <a:prstGeom prst="rect">
                   <a:avLst/>
@@ -11628,7 +12808,18 @@
                         <a:sysClr val="windowText" lastClr="000000"/>
                       </a:solidFill>
                     </a:rPr>
-                    <a:t>alt </a:t>
+                    <a:t>loop</a:t>
+                  </a:r>
+                </a:p>
+                <a:p>
+                  <a:pPr algn="ctr"/>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>[</a:t>
                   </a:r>
                   <a:r>
                     <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
@@ -11636,87 +12827,262 @@
                         <a:sysClr val="windowText" lastClr="000000"/>
                       </a:solidFill>
                     </a:rPr>
-                    <a:t>入力値</a:t>
+                    <a:t>入力値 </a:t>
                   </a:r>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>= - or </a:t>
+                  </a:r>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>文字</a:t>
+                  </a:r>
+                  <a:r>
+                    <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+                      <a:solidFill>
+                        <a:sysClr val="windowText" lastClr="000000"/>
+                      </a:solidFill>
+                    </a:rPr>
+                    <a:t>]</a:t>
+                  </a:r>
+                  <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:endParaRPr>
                 </a:p>
               </xdr:txBody>
             </xdr:sp>
           </xdr:grpSp>
         </xdr:grpSp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="110" name="テキスト ボックス 109">
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="438" name="グループ化 437">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC2DD7B5-D94F-E8B0-46A2-404BB6277987}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55ECEDBE-F487-8DCC-C6F6-8B0AFAF9C0BC}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
             <a:xfrm>
-              <a:off x="1581150" y="5734050"/>
-              <a:ext cx="1476375" cy="247650"/>
+              <a:off x="3137709" y="5237503"/>
+              <a:ext cx="1119967" cy="509039"/>
+              <a:chOff x="3078071" y="2150831"/>
+              <a:chExt cx="1123027" cy="513342"/>
             </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="9525" cmpd="sng">
+          </xdr:grpSpPr>
+          <xdr:grpSp>
+            <xdr:nvGrpSpPr>
+              <xdr:cNvPr id="439" name="グループ化 438">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2263C2CC-5AF9-313B-AA0B-B4847CA53E2F}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvGrpSpPr/>
+            </xdr:nvGrpSpPr>
+            <xdr:grpSpPr>
+              <a:xfrm>
+                <a:off x="3078071" y="2407127"/>
+                <a:ext cx="519226" cy="257046"/>
+                <a:chOff x="3111201" y="2183497"/>
+                <a:chExt cx="519226" cy="257046"/>
+              </a:xfrm>
+            </xdr:grpSpPr>
+            <xdr:cxnSp macro="">
+              <xdr:nvCxnSpPr>
+                <xdr:cNvPr id="441" name="直線矢印コネクタ 440">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C32DA063-EACD-34B6-A993-46F6E10C8338}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvCxnSpPr/>
+              </xdr:nvCxnSpPr>
+              <xdr:spPr>
+                <a:xfrm flipH="1">
+                  <a:off x="3111201" y="2440543"/>
+                  <a:ext cx="518937" cy="0"/>
+                </a:xfrm>
+                <a:prstGeom prst="straightConnector1">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1"/>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                  <a:round/>
+                  <a:headEnd type="none" w="med" len="med"/>
+                  <a:tailEnd type="triangle" w="med" len="med"/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:scrgbClr r="0" g="0" b="0"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="tx1"/>
+                </a:fontRef>
+              </xdr:style>
+            </xdr:cxnSp>
+            <xdr:cxnSp macro="">
+              <xdr:nvCxnSpPr>
+                <xdr:cNvPr id="442" name="直線コネクタ 441">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D85C6223-291B-DC48-4A6F-982C21048ED5}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvCxnSpPr/>
+              </xdr:nvCxnSpPr>
+              <xdr:spPr>
+                <a:xfrm>
+                  <a:off x="3630426" y="2184454"/>
+                  <a:ext cx="0" cy="254849"/>
+                </a:xfrm>
+                <a:prstGeom prst="line">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln>
+                  <a:headEnd type="none" w="med" len="med"/>
+                  <a:tailEnd type="none" w="med" len="med"/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="1">
+                  <a:schemeClr val="dk1"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:schemeClr val="dk1"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:schemeClr val="dk1"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="tx1"/>
+                </a:fontRef>
+              </xdr:style>
+            </xdr:cxnSp>
+            <xdr:cxnSp macro="">
+              <xdr:nvCxnSpPr>
+                <xdr:cNvPr id="443" name="直線コネクタ 442">
+                  <a:extLst>
+                    <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                      <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CC79B00-C233-563B-7FF9-6BB5CC6A8D5B}"/>
+                    </a:ext>
+                  </a:extLst>
+                </xdr:cNvPr>
+                <xdr:cNvCxnSpPr/>
+              </xdr:nvCxnSpPr>
+              <xdr:spPr>
+                <a:xfrm flipV="1">
+                  <a:off x="3122638" y="2183497"/>
+                  <a:ext cx="507789" cy="7327"/>
+                </a:xfrm>
+                <a:prstGeom prst="line">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:ln>
+                  <a:headEnd type="none" w="med" len="med"/>
+                  <a:tailEnd type="none" w="med" len="med"/>
+                </a:ln>
+              </xdr:spPr>
+              <xdr:style>
+                <a:lnRef idx="1">
+                  <a:schemeClr val="dk1"/>
+                </a:lnRef>
+                <a:fillRef idx="0">
+                  <a:schemeClr val="dk1"/>
+                </a:fillRef>
+                <a:effectRef idx="0">
+                  <a:schemeClr val="dk1"/>
+                </a:effectRef>
+                <a:fontRef idx="minor">
+                  <a:schemeClr val="tx1"/>
+                </a:fontRef>
+              </xdr:style>
+            </xdr:cxnSp>
+          </xdr:grpSp>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="440" name="テキスト ボックス 439">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{403E8982-C7F6-6198-0D43-DC27EDE9C085}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr txBox="1"/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="3267175" y="2150831"/>
+                <a:ext cx="933923" cy="318235"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
               <a:noFill/>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="ctr"/>
-              <a:r>
-                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-                <a:t>[</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-                <a:t>入力値 </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-                <a:t>= - or</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-                <a:t> 文字</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-                <a:t>]</a:t>
-              </a:r>
-              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
+              <a:ln w="9525" cmpd="sng">
+                <a:noFill/>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:lnRef>
+              <a:fillRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:scrgbClr r="0" g="0" b="0"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="dk1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr"/>
+                <a:r>
+                  <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+                  <a:t>エラー文</a:t>
+                </a:r>
+                <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
       </xdr:grpSp>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="103" name="グループ化 102">
+          <xdr:cNvPr id="427" name="グループ化 426">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30BB9757-9993-8DAF-5BC4-64447607E097}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0429E8F9-69F7-98DD-9F50-97E1C4C4E79D}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -11724,18 +13090,18 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="3137708" y="5418482"/>
-            <a:ext cx="1634318" cy="658468"/>
-            <a:chOff x="3078071" y="2333336"/>
-            <a:chExt cx="1638784" cy="664033"/>
+            <a:off x="3138673" y="6667501"/>
+            <a:ext cx="1185263" cy="489988"/>
+            <a:chOff x="3105202" y="2170044"/>
+            <a:chExt cx="1188502" cy="494129"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:grpSp>
           <xdr:nvGrpSpPr>
-            <xdr:cNvPr id="104" name="グループ化 103">
+            <xdr:cNvPr id="432" name="グループ化 431">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83D8EAF1-A1FB-5481-C887-BB2565BA70C3}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE64693E-08DA-3A7E-51F2-66A6A7384CC1}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11743,27 +13109,27 @@
           </xdr:nvGrpSpPr>
           <xdr:grpSpPr>
             <a:xfrm>
-              <a:off x="3078071" y="2407127"/>
-              <a:ext cx="519226" cy="257046"/>
-              <a:chOff x="3111201" y="2183497"/>
-              <a:chExt cx="519226" cy="257046"/>
+              <a:off x="3105202" y="2407127"/>
+              <a:ext cx="492095" cy="257046"/>
+              <a:chOff x="3138332" y="2183497"/>
+              <a:chExt cx="492095" cy="257046"/>
             </a:xfrm>
           </xdr:grpSpPr>
           <xdr:cxnSp macro="">
             <xdr:nvCxnSpPr>
-              <xdr:cNvPr id="106" name="直線矢印コネクタ 105">
+              <xdr:cNvPr id="434" name="直線矢印コネクタ 433">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA4EF714-FE4F-625D-FE3D-E41768EC8D76}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8FBF53C-EE88-AD09-76CC-337CE0FBE962}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
               <xdr:cNvCxnSpPr/>
             </xdr:nvCxnSpPr>
             <xdr:spPr>
-              <a:xfrm flipH="1">
-                <a:off x="3111201" y="2440543"/>
-                <a:ext cx="518937" cy="0"/>
+              <a:xfrm flipH="1" flipV="1">
+                <a:off x="3138332" y="2438246"/>
+                <a:ext cx="491805" cy="2297"/>
               </a:xfrm>
               <a:prstGeom prst="straightConnector1">
                 <a:avLst/>
@@ -11795,10 +13161,10 @@
           </xdr:cxnSp>
           <xdr:cxnSp macro="">
             <xdr:nvCxnSpPr>
-              <xdr:cNvPr id="107" name="直線コネクタ 106">
+              <xdr:cNvPr id="435" name="直線コネクタ 434">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69277635-6319-5CC4-6FFE-532853F1231E}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B406CFCE-5CC5-F397-9E1C-00902852CC05}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -11834,10 +13200,10 @@
           </xdr:cxnSp>
           <xdr:cxnSp macro="">
             <xdr:nvCxnSpPr>
-              <xdr:cNvPr id="108" name="直線コネクタ 107">
+              <xdr:cNvPr id="436" name="直線コネクタ 435">
                 <a:extLst>
                   <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E5A4DBA-C4C9-60BC-F9BF-D25605291230}"/>
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B03C3DF1-2A6F-B736-C6BA-CD10D7574E5B}"/>
                   </a:ext>
                 </a:extLst>
               </xdr:cNvPr>
@@ -11845,8 +13211,8 @@
             </xdr:nvCxnSpPr>
             <xdr:spPr>
               <a:xfrm flipV="1">
-                <a:off x="3122638" y="2183497"/>
-                <a:ext cx="507789" cy="7327"/>
+                <a:off x="3152956" y="2183497"/>
+                <a:ext cx="477471" cy="6874"/>
               </a:xfrm>
               <a:prstGeom prst="line">
                 <a:avLst/>
@@ -11874,10 +13240,10 @@
         </xdr:grpSp>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="105" name="テキスト ボックス 104">
+            <xdr:cNvPr id="433" name="テキスト ボックス 432">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77AC208D-09BC-FE6F-A1A2-E913F1BB0D6D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C783069E-D5D9-6582-E656-A120E299152E}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -11885,8 +13251,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3257624" y="2333336"/>
-              <a:ext cx="1459231" cy="664033"/>
+              <a:off x="3299791" y="2170044"/>
+              <a:ext cx="993913" cy="249721"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -11917,19 +13283,153 @@
               <a:pPr algn="ctr"/>
               <a:r>
                 <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-                <a:t>エラー文</a:t>
-              </a:r>
-              <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200"/>
-            </a:p>
-            <a:p>
-              <a:pPr algn="ctr"/>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
-                <a:t>選択肢表示に戻る</a:t>
+                <a:t>入力受付中</a:t>
               </a:r>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
+      </xdr:grpSp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="428" name="グループ化 427">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE31C49F-3E21-5C29-EA5A-6885D19AA724}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="3131305" y="6203708"/>
+            <a:ext cx="506405" cy="255969"/>
+            <a:chOff x="3122638" y="2183497"/>
+            <a:chExt cx="507789" cy="257046"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="429" name="直線矢印コネクタ 428">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BED3E151-F3FC-28A6-A8D5-3F73B146E5FB}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipH="1" flipV="1">
+              <a:off x="3142522" y="2439902"/>
+              <a:ext cx="487615" cy="641"/>
+            </a:xfrm>
+            <a:prstGeom prst="straightConnector1">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+              <a:headEnd type="none" w="med" len="med"/>
+              <a:tailEnd type="triangle" w="med" len="med"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="430" name="直線コネクタ 429">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27335867-E987-12C6-555D-A4A9B0A6914C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3630426" y="2184454"/>
+              <a:ext cx="0" cy="254849"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:headEnd type="none" w="med" len="med"/>
+              <a:tailEnd type="none" w="med" len="med"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="431" name="直線コネクタ 430">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{81BB222C-23E8-79DE-DD9A-059744AAF517}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm flipV="1">
+              <a:off x="3122638" y="2183497"/>
+              <a:ext cx="507789" cy="7327"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:headEnd type="none" w="med" len="med"/>
+              <a:tailEnd type="none" w="med" len="med"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
       </xdr:grpSp>
     </xdr:grpSp>
     <xdr:clientData/>

--- a/C++kadai/kadai04.xlsx
+++ b/C++kadai/kadai04.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\OracleLinux_8_5\home\integral\c++\repo\C++kadai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145E4922-0E11-435C-B723-5CD3622E8CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D2641A5-4BEC-49A0-8F61-13BA2AB938E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{6403A9A6-ECE0-481A-9546-5B7FA10BFF51}"/>
   </bookViews>
@@ -552,7 +552,7 @@
               <a:latin typeface="游ゴシック"/>
               <a:ea typeface="游ゴシック"/>
             </a:rPr>
-            <a:t>length</a:t>
+            <a:t>m_length</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1100" b="0" i="0">
@@ -653,7 +653,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>radius</a:t>
+            <a:t>m_radius</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
@@ -748,7 +748,7 @@
               <a:latin typeface="游ゴシック"/>
               <a:ea typeface="游ゴシック"/>
             </a:rPr>
-            <a:t>vertical</a:t>
+            <a:t>m_vertical</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1000" b="0" i="0">
@@ -797,7 +797,7 @@
               <a:latin typeface="游ゴシック"/>
               <a:ea typeface="游ゴシック"/>
             </a:rPr>
-            <a:t>width</a:t>
+            <a:t>m_width</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="ja-JP" altLang="ja-JP" sz="1000" b="0" i="0">
